--- a/data/trans_orig/P21D_3_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D_3_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos en 2023</t>
+          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,62 +765,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4296</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4246</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262761</t>
+          <t>262493</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298176</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561640</t>
+          <t>561590</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,97 +1073,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2960</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3816</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>767</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3974</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4889</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4018</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>655429</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>443381</t>
+          <t>443539</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1101726</t>
+          <t>1100855</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,97 +1416,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1291</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1577</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>328822</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328099</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>658650</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1759,97 +1759,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1246</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4222</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1246</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4243</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4247</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1246</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3900</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>406119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>513699</t>
+          <t>513720</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>921995</t>
+          <t>921648</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>558</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1659204</t>
+          <t>1659340</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1588799</t>
+          <t>1588411</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1593453</t>
+          <t>1593416</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3250334</t>
+          <t>3251318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3257008</t>
+          <t>3257138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/P21D_3_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D_3_R-Habitat-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>265835</t>
+          <t>287376</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262493</t>
+          <t>284278</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>565122</t>
+          <t>611536</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561590</t>
+          <t>607742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>565886</t>
+          <t>612283</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>565886</t>
+          <t>612283</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>565886</t>
+          <t>612283</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>565886</t>
+          <t>612283</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>446588</t>
+          <t>502645</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>443539</t>
+          <t>499575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1104977</t>
+          <t>972852</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1100855</t>
+          <t>969396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1902,27 +1902,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>516696</t>
+          <t>489470</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>513720</t>
+          <t>486777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>924649</t>
+          <t>922829</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>921648</t>
+          <t>919381</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,22 +2167,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2210,17 +2210,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1663014</t>
+          <t>1567527</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1659340</t>
+          <t>1563723</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,27 +2245,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1591961</t>
+          <t>1694923</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1588411</t>
+          <t>1691415</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1593416</t>
+          <t>1696372</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,22 +2280,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3254974</t>
+          <t>3262451</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3251318</t>
+          <t>3258533</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3257138</t>
+          <t>3264505</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
